--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/quillan/Documents/PhD-Notes/05_Teaching/01_BIO321_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD0C6C2-3189-914E-B986-A17ED72B8FCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A8331D-D7E8-6F4B-BA0B-8CC64C52BB73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17800" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34660" yWindow="1940" windowWidth="30240" windowHeight="17800" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sched" sheetId="1" r:id="rId1"/>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A8331D-D7E8-6F4B-BA0B-8CC64C52BB73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34660" yWindow="1940" windowWidth="30240" windowHeight="17800" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4640" yWindow="1660" windowWidth="30240" windowHeight="17800" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sched" sheetId="1" r:id="rId1"/>
